--- a/data/trans_orig/IP40-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP40-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según como llegan a fin de mes con los ingresos de su hogar en 2012 (tasa de respuesta: 97,0%)</t>
+          <t>Adultos según como llegan a fin de mes con los ingresos de su hogar en 2012 (tasa de respuesta: 97,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17967</t>
+          <t>17993</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22002</t>
+          <t>22200</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18734</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35508</t>
+          <t>35804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25177</t>
+          <t>24838</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41989</t>
+          <t>41938</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26868</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43419</t>
+          <t>44201</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55604</t>
+          <t>55638</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79435</t>
+          <t>81018</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35180</t>
+          <t>36733</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54166</t>
+          <t>54767</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38226</t>
+          <t>38317</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57524</t>
+          <t>58488</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79795</t>
+          <t>79240</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106620</t>
+          <t>106332</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15569</t>
+          <t>15142</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30448</t>
+          <t>30671</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>23502</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39395</t>
+          <t>39313</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42249</t>
+          <t>41616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63789</t>
+          <t>63826</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14551</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29438</t>
+          <t>29534</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>33448</t>
+          <t>33035</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>54631</t>
+          <t>53311</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>21709</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13750</t>
+          <t>13285</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27699</t>
+          <t>27328</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27122</t>
+          <t>27163</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44901</t>
+          <t>45966</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33780</t>
+          <t>33615</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51899</t>
+          <t>51761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32633</t>
+          <t>32899</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52409</t>
+          <t>51300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69967</t>
+          <t>70295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97386</t>
+          <t>96633</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51573</t>
+          <t>52481</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73454</t>
+          <t>72351</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63851</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86829</t>
+          <t>86586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>121710</t>
+          <t>121021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153629</t>
+          <t>152546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>36274</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55645</t>
+          <t>55902</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30454</t>
+          <t>31934</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50370</t>
+          <t>50441</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>73738</t>
+          <t>72168</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>100046</t>
+          <t>99014</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23960</t>
+          <t>24208</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40961</t>
+          <t>40057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28775</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>47234</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57801</t>
+          <t>57990</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82646</t>
+          <t>81475</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>914</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>7527</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18584</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11819</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24966</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39646</t>
+          <t>38275</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19153</t>
+          <t>19180</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33637</t>
+          <t>34348</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26302</t>
+          <t>26089</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43022</t>
+          <t>42680</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48787</t>
+          <t>49573</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71528</t>
+          <t>71166</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41058</t>
+          <t>40056</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59912</t>
+          <t>58916</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33719</t>
+          <t>34823</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53558</t>
+          <t>52487</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>80180</t>
+          <t>78906</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>105204</t>
+          <t>104780</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30246</t>
+          <t>30708</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47316</t>
+          <t>48125</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26116</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>42800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61588</t>
+          <t>61796</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85114</t>
+          <t>85363</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>18999</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34503</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24757</t>
+          <t>24878</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40404</t>
+          <t>40501</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47924</t>
+          <t>48514</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>70698</t>
+          <t>70381</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25825</t>
+          <t>24716</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44254</t>
+          <t>42660</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29283</t>
+          <t>28941</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48143</t>
+          <t>48182</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>58693</t>
+          <t>58511</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>86503</t>
+          <t>85597</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>42141</t>
+          <t>41458</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>64463</t>
+          <t>62489</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>39471</t>
+          <t>39023</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>59878</t>
+          <t>60021</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>87814</t>
+          <t>86556</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>118044</t>
+          <t>116130</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52879</t>
+          <t>52424</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>75352</t>
+          <t>75954</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44946</t>
+          <t>44866</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>66137</t>
+          <t>67044</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>104358</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>134527</t>
+          <t>135496</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26992</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47747</t>
+          <t>46830</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26377</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44708</t>
+          <t>43780</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58511</t>
+          <t>57580</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>84504</t>
+          <t>84442</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27601</t>
+          <t>27101</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16345</t>
+          <t>16535</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32569</t>
+          <t>32096</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32359</t>
+          <t>32748</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>54530</t>
+          <t>53988</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>12573</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12347</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>21515</t>
+          <t>21366</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -4025,12 +4025,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>59868</t>
+          <t>59835</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>88874</t>
+          <t>86560</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>76279</t>
+          <t>76171</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>106078</t>
+          <t>104941</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>144977</t>
+          <t>143641</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>184708</t>
+          <t>185964</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>135553</t>
+          <t>136507</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>173318</t>
+          <t>168659</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>140214</t>
+          <t>139808</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>175205</t>
+          <t>175891</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>284671</t>
+          <t>285847</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>337139</t>
+          <t>336994</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -4251,12 +4251,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>200067</t>
+          <t>200493</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>239366</t>
+          <t>239882</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>199395</t>
+          <t>200468</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>239830</t>
+          <t>240844</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>412440</t>
+          <t>413216</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>470784</t>
+          <t>471302</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>124938</t>
+          <t>127095</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>160360</t>
+          <t>159388</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>122897</t>
+          <t>122080</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>157793</t>
+          <t>156610</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>255039</t>
+          <t>257222</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>304220</t>
+          <t>303775</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4477,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>85238</t>
+          <t>83187</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>116007</t>
+          <t>111461</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>99408</t>
+          <t>98651</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>131142</t>
+          <t>131094</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>190306</t>
+          <t>191498</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>233770</t>
+          <t>236707</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según como llegan a fin de mes con los ingresos de su hogar en 2016 (tasa de respuesta: 98,82%)</t>
+          <t>Adultos según como llegan a fin de mes con los ingresos de su hogar en 2016 (tasa de respuesta: 98,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18810</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30941</t>
+          <t>31072</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26550</t>
+          <t>26024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45968</t>
+          <t>45001</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27486</t>
+          <t>27081</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44948</t>
+          <t>43496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19679</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35291</t>
+          <t>35719</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50231</t>
+          <t>51669</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74510</t>
+          <t>75063</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>26650</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43235</t>
+          <t>42933</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>31558</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51023</t>
+          <t>50323</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63731</t>
+          <t>64382</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89074</t>
+          <t>88683</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20114</t>
+          <t>20277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36552</t>
+          <t>36062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26679</t>
+          <t>27071</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44541</t>
+          <t>44894</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51108</t>
+          <t>50478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75164</t>
+          <t>75421</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26964</t>
+          <t>27611</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26718</t>
+          <t>27113</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30596</t>
+          <t>29488</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50375</t>
+          <t>49340</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6692</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10673</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14750</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>28375</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21490</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37117</t>
+          <t>37065</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39757</t>
+          <t>39537</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60776</t>
+          <t>59973</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28886</t>
+          <t>29686</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46050</t>
+          <t>46705</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37828</t>
+          <t>38218</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57791</t>
+          <t>57454</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6010,47 +6010,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>17,13%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>25,75%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>84378</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>72476</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>97640</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>19,74%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>16,96%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>25,9%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>84378</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>71742</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>98039</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>19,74%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>16,79%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59061</t>
+          <t>59517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79620</t>
+          <t>80571</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51068</t>
+          <t>50192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71645</t>
+          <t>71127</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114928</t>
+          <t>115391</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>145354</t>
+          <t>145769</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36857</t>
+          <t>36886</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55587</t>
+          <t>54867</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46580</t>
+          <t>46820</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67778</t>
+          <t>68656</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>88860</t>
+          <t>88589</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>116486</t>
+          <t>117354</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21939</t>
+          <t>20664</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37803</t>
+          <t>37291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19555</t>
+          <t>19944</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35209</t>
+          <t>35676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45821</t>
+          <t>44889</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67358</t>
+          <t>68607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>17264</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>18287</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34070</t>
+          <t>34510</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21445</t>
+          <t>21190</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37009</t>
+          <t>36236</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29014</t>
+          <t>29166</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40248</t>
+          <t>40949</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61280</t>
+          <t>61121</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32253</t>
+          <t>31311</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48251</t>
+          <t>47598</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31802</t>
+          <t>33284</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50733</t>
+          <t>52618</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>67302</t>
+          <t>69566</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>92365</t>
+          <t>93060</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30857</t>
+          <t>31040</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46262</t>
+          <t>47291</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35650</t>
+          <t>36165</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53702</t>
+          <t>53745</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71418</t>
+          <t>71756</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97042</t>
+          <t>97785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>28214</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43772</t>
+          <t>44624</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33988</t>
+          <t>34417</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52356</t>
+          <t>51696</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66852</t>
+          <t>65838</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>90212</t>
+          <t>89598</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -7324,12 +7324,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19704</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37248</t>
+          <t>37469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7452,12 +7452,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21295</t>
+          <t>21850</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38422</t>
+          <t>37922</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45284</t>
+          <t>45867</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>69124</t>
+          <t>69828</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -7550,12 +7550,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44649</t>
+          <t>43435</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>65243</t>
+          <t>64444</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7585,12 +7585,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>43099</t>
+          <t>43100</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>63040</t>
+          <t>63585</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>92266</t>
+          <t>92233</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>122205</t>
+          <t>121335</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -7663,12 +7663,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>45700</t>
+          <t>45689</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>67157</t>
+          <t>67190</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45427</t>
+          <t>46081</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>66533</t>
+          <t>67349</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>99055</t>
+          <t>98830</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>127709</t>
+          <t>129227</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24899</t>
+          <t>25656</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42528</t>
+          <t>44073</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28974</t>
+          <t>28660</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46842</t>
+          <t>47167</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58481</t>
+          <t>59040</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>84511</t>
+          <t>83377</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -7889,12 +7889,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>24396</t>
+          <t>24369</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42003</t>
+          <t>42587</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18516</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>34097</t>
+          <t>34545</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>46221</t>
+          <t>47027</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>71355</t>
+          <t>70964</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7974,12 +7974,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13028</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12421</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>22486</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -8232,12 +8232,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>60915</t>
+          <t>60459</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>86303</t>
+          <t>86938</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8267,12 +8267,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>80108</t>
+          <t>78152</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>109800</t>
+          <t>108435</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>147568</t>
+          <t>145951</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>187764</t>
+          <t>185976</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8345,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>137824</t>
+          <t>136679</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>173347</t>
+          <t>173983</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>130992</t>
+          <t>132477</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>168051</t>
+          <t>166536</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>280353</t>
+          <t>278243</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>331754</t>
+          <t>327684</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -8458,12 +8458,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>180292</t>
+          <t>180552</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>218531</t>
+          <t>217622</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>179120</t>
+          <t>181088</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>220435</t>
+          <t>221008</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>368336</t>
+          <t>369390</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>426658</t>
+          <t>426279</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8543,12 +8543,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>129042</t>
+          <t>128015</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>162580</t>
+          <t>161532</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>155211</t>
+          <t>156139</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>194400</t>
+          <t>193412</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8621,12 +8621,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>294078</t>
+          <t>294173</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>345331</t>
+          <t>344930</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -8684,12 +8684,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>100496</t>
+          <t>101180</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>130854</t>
+          <t>133191</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8699,12 +8699,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>97531</t>
+          <t>97817</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>131330</t>
+          <t>132377</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8734,47 +8734,47 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
+          <t>17,92%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>230757</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>207773</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>254953</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>16,1%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>14,49%</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
           <t>17,78%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>230757</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>206734</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>253923</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>16,1%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>14,42%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según como llegan a fin de mes con los ingresos de su hogar en 2023 (tasa de respuesta: 99,57%)</t>
+          <t>Adultos según como llegan a fin de mes con los ingresos de su hogar en 2023 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9146,12 +9146,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>400</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -9259,12 +9259,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20347</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33123</t>
+          <t>32298</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39050</t>
+          <t>39654</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62007</t>
+          <t>60063</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -9372,12 +9372,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29102</t>
+          <t>29641</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>45983</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9387,12 +9387,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33523</t>
+          <t>34519</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58296</t>
+          <t>58959</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67918</t>
+          <t>70247</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98417</t>
+          <t>99310</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -9485,12 +9485,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>23904</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38868</t>
+          <t>39314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9500,12 +9500,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39212</t>
+          <t>39209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74483</t>
+          <t>73349</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68456</t>
+          <t>68326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108434</t>
+          <t>109538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9570,12 +9570,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,46%</t>
         </is>
       </c>
     </row>
@@ -9598,12 +9598,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>16589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18151</t>
+          <t>17589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9648,12 +9648,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>15299</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30529</t>
+          <t>29614</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9683,12 +9683,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -9711,12 +9711,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>9597</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13646</t>
+          <t>13176</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9761,12 +9761,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18283</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -9941,12 +9941,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9956,12 +9956,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>787</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9991,12 +9991,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>10909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10026,12 +10026,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -10054,12 +10054,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25440</t>
+          <t>26077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43461</t>
+          <t>44221</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10069,12 +10069,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33207</t>
+          <t>33173</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54199</t>
+          <t>54038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10104,12 +10104,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63010</t>
+          <t>63350</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>92462</t>
+          <t>91371</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10139,12 +10139,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -10167,12 +10167,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51247</t>
+          <t>51765</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73288</t>
+          <t>73965</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10182,12 +10182,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78674</t>
+          <t>80249</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108375</t>
+          <t>108538</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10217,12 +10217,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140625</t>
+          <t>139949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176097</t>
+          <t>177237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10252,12 +10252,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56002</t>
+          <t>55173</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80011</t>
+          <t>80448</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10295,12 +10295,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61090</t>
+          <t>61052</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90821</t>
+          <t>90339</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10330,12 +10330,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122259</t>
+          <t>123971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162740</t>
+          <t>161913</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10365,12 +10365,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -10393,12 +10393,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19583</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32864</t>
+          <t>32934</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10443,12 +10443,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10463,12 +10463,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27686</t>
+          <t>27937</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>48280</t>
+          <t>47497</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10478,12 +10478,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -10506,12 +10506,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>13016</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10541,12 +10541,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20195</t>
+          <t>19121</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10556,12 +10556,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28605</t>
+          <t>27612</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10591,12 +10591,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -10736,12 +10736,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -10849,12 +10849,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20091</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45943</t>
+          <t>44658</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10884,12 +10884,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33586</t>
+          <t>33710</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58237</t>
+          <t>58508</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10899,12 +10899,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10919,12 +10919,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59667</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94709</t>
+          <t>96160</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -10962,12 +10962,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27922</t>
+          <t>26985</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60154</t>
+          <t>60954</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10997,12 +10997,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36801</t>
+          <t>36785</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61136</t>
+          <t>61786</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11012,12 +11012,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71732</t>
+          <t>71464</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>114940</t>
+          <t>113565</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11047,12 +11047,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -11075,12 +11075,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28115</t>
+          <t>29832</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>62006</t>
+          <t>61874</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11110,12 +11110,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50150</t>
+          <t>49081</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75923</t>
+          <t>76156</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11125,12 +11125,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11145,12 +11145,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>83057</t>
+          <t>82428</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>130220</t>
+          <t>128574</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11160,12 +11160,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -11188,12 +11188,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20809</t>
+          <t>20528</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101934</t>
+          <t>102999</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12771</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28967</t>
+          <t>29097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11258,12 +11258,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38781</t>
+          <t>38699</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143466</t>
+          <t>137891</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11273,12 +11273,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>37,9%</t>
         </is>
       </c>
     </row>
@@ -11301,12 +11301,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t>8355</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11316,12 +11316,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11371,12 +11371,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18731</t>
+          <t>18496</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>10580</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -11644,12 +11644,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27800</t>
+          <t>28347</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45785</t>
+          <t>45566</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11659,12 +11659,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11679,12 +11679,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32546</t>
+          <t>32685</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>52037</t>
+          <t>52198</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11714,12 +11714,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>66720</t>
+          <t>66161</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>91932</t>
+          <t>92405</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -11757,12 +11757,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>38304</t>
+          <t>38318</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>57778</t>
+          <t>57473</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11772,12 +11772,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11792,12 +11792,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>47325</t>
+          <t>47059</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>69717</t>
+          <t>70481</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>91162</t>
+          <t>90369</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>121583</t>
+          <t>120563</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -11870,12 +11870,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38232</t>
+          <t>39030</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59873</t>
+          <t>59603</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11905,12 +11905,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>39230</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60812</t>
+          <t>60315</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11940,12 +11940,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>82650</t>
+          <t>83428</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>112766</t>
+          <t>114513</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -11983,12 +11983,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>11181</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24244</t>
+          <t>24374</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14333</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31021</t>
+          <t>30893</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12053,12 +12053,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28609</t>
+          <t>28830</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49464</t>
+          <t>49227</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -12096,12 +12096,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>13692</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12131,12 +12131,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12166,12 +12166,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19341</t>
+          <t>20048</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16366</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10844</t>
+          <t>10480</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22525</t>
+          <t>22687</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -12439,12 +12439,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>108781</t>
+          <t>111944</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>149696</t>
+          <t>150227</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12454,12 +12454,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12474,12 +12474,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>131114</t>
+          <t>130506</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>171846</t>
+          <t>173634</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12509,12 +12509,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>254183</t>
+          <t>250516</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>312705</t>
+          <t>309513</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -12552,12 +12552,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>164418</t>
+          <t>165898</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>217003</t>
+          <t>216386</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12567,12 +12567,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12587,12 +12587,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>221614</t>
+          <t>224872</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>273590</t>
+          <t>273839</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12622,12 +12622,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>401717</t>
+          <t>403188</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>476097</t>
+          <t>478250</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>162374</t>
+          <t>165908</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>216003</t>
+          <t>218261</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12680,12 +12680,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12700,12 +12700,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>210580</t>
+          <t>210854</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>268754</t>
+          <t>267771</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12735,12 +12735,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>390372</t>
+          <t>394597</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>472528</t>
+          <t>472332</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -12778,12 +12778,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>59546</t>
+          <t>59710</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>182741</t>
+          <t>170062</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12813,12 +12813,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>62414</t>
+          <t>61765</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>91767</t>
+          <t>91154</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12848,12 +12848,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>133403</t>
+          <t>134088</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>251288</t>
+          <t>269245</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -12891,12 +12891,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>18164</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>35241</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12906,12 +12906,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12926,12 +12926,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>40344</t>
+          <t>41444</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12941,12 +12941,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12961,12 +12961,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>42160</t>
+          <t>42998</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>70139</t>
+          <t>69305</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12976,12 +12976,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
